--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/bank_partner_contracts.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/bank_partner_contracts.xlsx
@@ -490,15 +490,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FX</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.63</v>
+        <v>1.68</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-03-21</t>
         </is>
       </c>
     </row>
@@ -515,15 +515,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Cash mgmt</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.22</v>
+        <v>2.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2028-02-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -540,15 +540,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cash mgmt</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.57</v>
+        <v>2.41</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2028-04-02</t>
+          <t>2026-11-28</t>
         </is>
       </c>
     </row>
@@ -565,15 +565,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Debt</t>
+          <t>FX</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.87</v>
+        <v>0.27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2028-06-22</t>
+          <t>2027-08-29</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.14</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027-12-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2028-05-01</t>
+          <t>2027-02-18</t>
         </is>
       </c>
     </row>
@@ -640,15 +640,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FX</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.11</v>
+        <v>0.15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2028-04-17</t>
+          <t>2027-01-20</t>
         </is>
       </c>
     </row>
@@ -665,15 +665,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FX</t>
+          <t>Debt</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-11-29</t>
         </is>
       </c>
     </row>
@@ -694,11 +694,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.52</v>
+        <v>2.29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2028-11-19</t>
+          <t>2027-10-05</t>
         </is>
       </c>
     </row>
@@ -715,15 +715,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Debt</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.57</v>
+        <v>2.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-05-24</t>
         </is>
       </c>
     </row>
